--- a/endpoint_excels/iss__engines__engine__markets__market__securities__security.xlsx
+++ b/endpoint_excels/iss__engines__engine__markets__market__securities__security.xlsx
@@ -11,6 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marketdata" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataversion" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marketdata_yields" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COLUMN_DOCS" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,16 +32,26 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -54,14 +65,34 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -137,6 +168,193 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TBL_01_iss__engines__engi" displayName="TBL_01_iss__engines__engi" ref="A1:AT3" headerRowCount="1">
+  <autoFilter ref="A1:AT3"/>
+  <tableColumns count="46">
+    <tableColumn id="1" name="REQUEST_URL"/>
+    <tableColumn id="2" name="SECID"/>
+    <tableColumn id="3" name="BOARDID"/>
+    <tableColumn id="4" name="SHORTNAME"/>
+    <tableColumn id="5" name="PREVWAPRICE"/>
+    <tableColumn id="6" name="YIELDATPREVWAPRICE"/>
+    <tableColumn id="7" name="COUPONVALUE"/>
+    <tableColumn id="8" name="NEXTCOUPON"/>
+    <tableColumn id="9" name="ACCRUEDINT"/>
+    <tableColumn id="10" name="PREVPRICE"/>
+    <tableColumn id="11" name="LOTSIZE"/>
+    <tableColumn id="12" name="FACEVALUE"/>
+    <tableColumn id="13" name="BOARDNAME"/>
+    <tableColumn id="14" name="STATUS"/>
+    <tableColumn id="15" name="MATDATE"/>
+    <tableColumn id="16" name="DECIMALS"/>
+    <tableColumn id="17" name="COUPONPERIOD"/>
+    <tableColumn id="18" name="ISSUESIZE"/>
+    <tableColumn id="19" name="PREVLEGALCLOSEPRICE"/>
+    <tableColumn id="20" name="PREVDATE"/>
+    <tableColumn id="21" name="SECNAME"/>
+    <tableColumn id="22" name="REMARKS"/>
+    <tableColumn id="23" name="MARKETCODE"/>
+    <tableColumn id="24" name="INSTRID"/>
+    <tableColumn id="25" name="SECTORID"/>
+    <tableColumn id="26" name="MINSTEP"/>
+    <tableColumn id="27" name="FACEUNIT"/>
+    <tableColumn id="28" name="BUYBACKPRICE"/>
+    <tableColumn id="29" name="BUYBACKDATE"/>
+    <tableColumn id="30" name="ISIN"/>
+    <tableColumn id="31" name="LATNAME"/>
+    <tableColumn id="32" name="REGNUMBER"/>
+    <tableColumn id="33" name="CURRENCYID"/>
+    <tableColumn id="34" name="ISSUESIZEPLACED"/>
+    <tableColumn id="35" name="LISTLEVEL"/>
+    <tableColumn id="36" name="SECTYPE"/>
+    <tableColumn id="37" name="COUPONPERCENT"/>
+    <tableColumn id="38" name="OFFERDATE"/>
+    <tableColumn id="39" name="SETTLEDATE"/>
+    <tableColumn id="40" name="LOTVALUE"/>
+    <tableColumn id="41" name="FACEVALUEONSETTLEDATE"/>
+    <tableColumn id="42" name="CALLOPTIONDATE"/>
+    <tableColumn id="43" name="PUTOPTIONDATE"/>
+    <tableColumn id="44" name="DATEYIELDFROMISSUER"/>
+    <tableColumn id="45" name="BONDTYPE"/>
+    <tableColumn id="46" name="BONDSUBTYPE"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TBL_02_iss__engines__engi" displayName="TBL_02_iss__engines__engi" ref="A1:BL3" headerRowCount="1">
+  <autoFilter ref="A1:BL3"/>
+  <tableColumns count="64">
+    <tableColumn id="1" name="REQUEST_URL"/>
+    <tableColumn id="2" name="SECID"/>
+    <tableColumn id="3" name="BID"/>
+    <tableColumn id="4" name="BIDDEPTH"/>
+    <tableColumn id="5" name="OFFER"/>
+    <tableColumn id="6" name="OFFERDEPTH"/>
+    <tableColumn id="7" name="SPREAD"/>
+    <tableColumn id="8" name="BIDDEPTHT"/>
+    <tableColumn id="9" name="OFFERDEPTHT"/>
+    <tableColumn id="10" name="OPEN"/>
+    <tableColumn id="11" name="LOW"/>
+    <tableColumn id="12" name="HIGH"/>
+    <tableColumn id="13" name="LAST"/>
+    <tableColumn id="14" name="LASTCHANGE"/>
+    <tableColumn id="15" name="LASTCHANGEPRCNT"/>
+    <tableColumn id="16" name="QTY"/>
+    <tableColumn id="17" name="VALUE"/>
+    <tableColumn id="18" name="YIELD"/>
+    <tableColumn id="19" name="VALUE_USD"/>
+    <tableColumn id="20" name="WAPRICE"/>
+    <tableColumn id="21" name="LASTCNGTOLASTWAPRICE"/>
+    <tableColumn id="22" name="WAPTOPREVWAPRICEPRCNT"/>
+    <tableColumn id="23" name="WAPTOPREVWAPRICE"/>
+    <tableColumn id="24" name="YIELDATWAPRICE"/>
+    <tableColumn id="25" name="YIELDTOPREVYIELD"/>
+    <tableColumn id="26" name="CLOSEYIELD"/>
+    <tableColumn id="27" name="CLOSEPRICE"/>
+    <tableColumn id="28" name="MARKETPRICETODAY"/>
+    <tableColumn id="29" name="MARKETPRICE"/>
+    <tableColumn id="30" name="LASTTOPREVPRICE"/>
+    <tableColumn id="31" name="NUMTRADES"/>
+    <tableColumn id="32" name="VOLTODAY"/>
+    <tableColumn id="33" name="VALTODAY"/>
+    <tableColumn id="34" name="VALTODAY_USD"/>
+    <tableColumn id="35" name="BOARDID"/>
+    <tableColumn id="36" name="TRADINGSTATUS"/>
+    <tableColumn id="37" name="UPDATETIME"/>
+    <tableColumn id="38" name="DURATION"/>
+    <tableColumn id="39" name="NUMBIDS"/>
+    <tableColumn id="40" name="NUMOFFERS"/>
+    <tableColumn id="41" name="CHANGE"/>
+    <tableColumn id="42" name="TIME"/>
+    <tableColumn id="43" name="HIGHBID"/>
+    <tableColumn id="44" name="LOWOFFER"/>
+    <tableColumn id="45" name="PRICEMINUSPREVWAPRICE"/>
+    <tableColumn id="46" name="LASTBID"/>
+    <tableColumn id="47" name="LASTOFFER"/>
+    <tableColumn id="48" name="LCURRENTPRICE"/>
+    <tableColumn id="49" name="LCLOSEPRICE"/>
+    <tableColumn id="50" name="MARKETPRICE2"/>
+    <tableColumn id="51" name="OPENPERIODPRICE"/>
+    <tableColumn id="52" name="SEQNUM"/>
+    <tableColumn id="53" name="SYSTIME"/>
+    <tableColumn id="54" name="VALTODAY_RUR"/>
+    <tableColumn id="55" name="IRICPICLOSE"/>
+    <tableColumn id="56" name="BEICLOSE"/>
+    <tableColumn id="57" name="CBRCLOSE"/>
+    <tableColumn id="58" name="YIELDTOOFFER"/>
+    <tableColumn id="59" name="YIELDLASTCOUPON"/>
+    <tableColumn id="60" name="TRADINGSESSION"/>
+    <tableColumn id="61" name="CALLOPTIONYIELD"/>
+    <tableColumn id="62" name="CALLOPTIONDURATION"/>
+    <tableColumn id="63" name="ZSPREAD"/>
+    <tableColumn id="64" name="ZSPREADATWAPRICE"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TBL_03_iss__engines__engi" displayName="TBL_03_iss__engines__engi" ref="A1:F3" headerRowCount="1">
+  <autoFilter ref="A1:F3"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="data_version"/>
+    <tableColumn id="4" name="seqnum"/>
+    <tableColumn id="5" name="trade_date"/>
+    <tableColumn id="6" name="trade_session_date"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TBL_04_iss__engines__engi" displayName="TBL_04_iss__engines__engi" ref="A1:W3" headerRowCount="1">
+  <autoFilter ref="A1:W3"/>
+  <tableColumns count="23">
+    <tableColumn id="1" name="REQUEST_URL"/>
+    <tableColumn id="2" name="SECID"/>
+    <tableColumn id="3" name="BOARDID"/>
+    <tableColumn id="4" name="PRICE"/>
+    <tableColumn id="5" name="YIELDDATE"/>
+    <tableColumn id="6" name="ZCYCMOMENT"/>
+    <tableColumn id="7" name="YIELDDATETYPE"/>
+    <tableColumn id="8" name="EFFECTIVEYIELD"/>
+    <tableColumn id="9" name="DURATION"/>
+    <tableColumn id="10" name="ZSPREADBP"/>
+    <tableColumn id="11" name="GSPREADBP"/>
+    <tableColumn id="12" name="WAPRICE"/>
+    <tableColumn id="13" name="EFFECTIVEYIELDWAPRICE"/>
+    <tableColumn id="14" name="DURATIONWAPRICE"/>
+    <tableColumn id="15" name="IR"/>
+    <tableColumn id="16" name="ICPI"/>
+    <tableColumn id="17" name="BEI"/>
+    <tableColumn id="18" name="CBR"/>
+    <tableColumn id="19" name="YIELDTOOFFER"/>
+    <tableColumn id="20" name="YIELDLASTCOUPON"/>
+    <tableColumn id="21" name="TRADEMOMENT"/>
+    <tableColumn id="22" name="SEQNUM"/>
+    <tableColumn id="23" name="SYSTIME"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="ENDPOINT_COLUMN_DOCS" displayName="ENDPOINT_COLUMN_DOCS" ref="A1:C140" headerRowCount="1">
+  <autoFilter ref="A1:C140"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="SHEET_NAME"/>
+    <tableColumn id="2" name="COLUMN_NAME"/>
+    <tableColumn id="3" name="DESCRIPTION_RU"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -430,8 +648,56 @@
   </sheetPr>
   <dimension ref="A1:AT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="31" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="23" customWidth="1" min="41" max="41"/>
+    <col width="16" customWidth="1" min="42" max="42"/>
+    <col width="15" customWidth="1" min="43" max="43"/>
+    <col width="21" customWidth="1" min="44" max="44"/>
+    <col width="26" customWidth="1" min="45" max="45"/>
+    <col width="14" customWidth="1" min="46" max="46"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>REQUEST_URL</t>
@@ -664,344 +930,344 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>TQOB</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>ОФЗ 26238</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>59.061</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="2" t="n">
         <v>13.95</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="2" t="n">
         <v>35.4</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>14.78</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>59.549</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Т+: Гособлигации - безадрес.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>2041-05-15</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>182</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="2" t="n">
         <v>750000000</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="2" t="n">
         <v>59.549</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>ОФЗ-ПД 26238 15/05/2041</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>FNDT</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>GOFZ</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="n">
         <v>0.001</v>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>SUR</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>0000-00-00</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>RU000A1038V6</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>OFZ-PD 26238</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>26238RMFS</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>SUR</t>
         </is>
       </c>
-      <c r="AH2" t="n">
+      <c r="AH2" s="2" t="n">
         <v>722071798</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AI2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AK2" t="n">
+      <c r="AK2" s="2" t="n">
         <v>7.1</v>
       </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr">
+      <c r="AL2" s="2" t="inlineStr"/>
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="AN2" t="n">
+      <c r="AN2" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AO2" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr"/>
+      <c r="AQ2" s="2" t="inlineStr"/>
+      <c r="AR2" s="2" t="inlineStr"/>
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>Фикс с известным купоном</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AT2" s="2" t="inlineStr">
         <is>
           <t>До погашения</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>ИАДОМ 1P13</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>98.12</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="2" t="n">
         <v>18.76</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="2" t="n">
         <v>7.05</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>4.55</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="2" t="n">
         <v>98.12</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="2" t="n">
         <v>498.52</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Т+: Облигации - безадрес.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>2031-10-28</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="2" t="n">
         <v>5353129</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="2" t="n">
         <v>98.12</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>ДОМ.РФ Ипотечный агент БО 1P13</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>FNDT</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>EICB</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="n">
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>SUR</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>2031-10-28</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE3" s="2" t="inlineStr">
         <is>
           <t>DOM.RF Mortgage agent BO 1P13</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF3" s="2" t="inlineStr">
         <is>
           <t>4B02-13-00307-R-001P</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG3" s="2" t="inlineStr">
         <is>
           <t>SUR</t>
         </is>
       </c>
-      <c r="AH3" t="n">
+      <c r="AH3" s="2" t="n">
         <v>5353129</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AI3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AJ3" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AK3" t="n">
+      <c r="AK3" s="2" t="n">
         <v>16.65</v>
       </c>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr">
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr">
         <is>
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="AN3" t="n">
+      <c r="AN3" s="2" t="n">
         <v>498.52</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AO3" s="2" t="n">
         <v>498.52</v>
       </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr">
+      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr">
         <is>
           <t>Флоатер</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AT3" s="2" t="inlineStr">
         <is>
           <t>До погашения</t>
         </is>
@@ -1009,6 +1275,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1020,8 +1289,74 @@
   </sheetPr>
   <dimension ref="A1:BL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="15" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="23" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="11" customWidth="1" min="47" max="47"/>
+    <col width="15" customWidth="1" min="48" max="48"/>
+    <col width="13" customWidth="1" min="49" max="49"/>
+    <col width="14" customWidth="1" min="50" max="50"/>
+    <col width="17" customWidth="1" min="51" max="51"/>
+    <col width="16" customWidth="1" min="52" max="52"/>
+    <col width="21" customWidth="1" min="53" max="53"/>
+    <col width="14" customWidth="1" min="54" max="54"/>
+    <col width="13" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="14" customWidth="1" min="58" max="58"/>
+    <col width="17" customWidth="1" min="59" max="59"/>
+    <col width="16" customWidth="1" min="60" max="60"/>
+    <col width="17" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="18" customWidth="1" min="64" max="64"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>REQUEST_URL</t>
@@ -1344,345 +1679,348 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>60.108</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>60.123</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="H2" t="n">
-        <v>892596</v>
-      </c>
-      <c r="I2" t="n">
-        <v>433850</v>
-      </c>
-      <c r="J2" t="n">
+      <c r="C2" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="n">
+        <v>60.001</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>796970</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>470445</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>59.697</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="2" t="n">
         <v>59.605</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>60.6</v>
       </c>
-      <c r="M2" t="n">
-        <v>60.123</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.003</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="M2" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P2" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>16233.21</v>
-      </c>
-      <c r="R2" t="n">
+      <c r="P2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>13.72</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>15.55</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>60.12</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="X2" s="2" t="n">
         <v>13.69</v>
       </c>
-      <c r="S2" t="n">
-        <v>210.29</v>
-      </c>
-      <c r="T2" t="n">
-        <v>60.124</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.062</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.063</v>
-      </c>
-      <c r="X2" t="n">
-        <v>13.69</v>
-      </c>
-      <c r="Y2" t="n">
+      <c r="Y2" s="2" t="n">
         <v>-0.26</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="Z2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="n">
         <v>59.045</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>34089</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2811541</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1690411219</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21898107</v>
-      </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AD2" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AE2" s="2" t="n">
+        <v>36712</v>
+      </c>
+      <c r="AF2" s="2" t="n">
+        <v>3024866</v>
+      </c>
+      <c r="AG2" s="2" t="n">
+        <v>1818540832</v>
+      </c>
+      <c r="AH2" s="2" t="n">
+        <v>23557937</v>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>TQOB</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>16:10:29</t>
-        </is>
-      </c>
-      <c r="AL2" t="n">
+      <c r="AK2" s="2" t="inlineStr">
+        <is>
+          <t>17:29:13</t>
+        </is>
+      </c>
+      <c r="AL2" s="2" t="n">
         <v>2788</v>
       </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>16:10:29</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>1.062</v>
-      </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>60.068</v>
-      </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
+      <c r="AM2" s="2" t="inlineStr"/>
+      <c r="AN2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>17:29:13</t>
+        </is>
+      </c>
+      <c r="AQ2" s="2" t="inlineStr"/>
+      <c r="AR2" s="2" t="inlineStr"/>
+      <c r="AS2" s="2" t="n">
+        <v>0.9389999999999999</v>
+      </c>
+      <c r="AT2" s="2" t="inlineStr"/>
+      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="n">
+        <v>60.002</v>
+      </c>
+      <c r="AW2" s="2" t="inlineStr"/>
+      <c r="AX2" s="2" t="inlineStr"/>
+      <c r="AY2" s="2" t="n">
         <v>59.697</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>20260216162529</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:29</t>
-        </is>
-      </c>
-      <c r="BB2" t="n">
-        <v>1690411219</v>
-      </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr">
+      <c r="AZ2" s="2" t="n">
+        <v>20260216174414</v>
+      </c>
+      <c r="BA2" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:14</t>
+        </is>
+      </c>
+      <c r="BB2" s="2" t="n">
+        <v>1818540832</v>
+      </c>
+      <c r="BC2" s="2" t="inlineStr"/>
+      <c r="BD2" s="2" t="inlineStr"/>
+      <c r="BE2" s="2" t="inlineStr"/>
+      <c r="BF2" s="2" t="inlineStr"/>
+      <c r="BG2" s="2" t="inlineStr"/>
+      <c r="BH2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="n">
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="BL2" s="2" t="n">
         <v>-0.5</v>
       </c>
-      <c r="BL2" t="n">
-        <v>-0.5</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>98.06</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n">
         <v>98.11</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="2" t="n">
         <v>6166</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>6314</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="2" t="n">
         <v>98.06999999999999</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="2" t="n">
         <v>98.06</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="2" t="n">
         <v>98.06999999999999</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="2" t="n">
         <v>98.06</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>488.85</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="2" t="n">
         <v>6.33</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="2" t="n">
         <v>98.06999999999999</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3" s="2" t="n">
         <v>-0.06</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3" s="2" t="n">
         <v>-0.05</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W3" s="2" t="n">
         <v>-0.05</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="Z3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="n">
         <v>97.94</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AD3" s="2" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AE3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AF3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AG3" s="2" t="n">
         <v>978</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AH3" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AI3" s="2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AJ3" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AK3" s="2" t="inlineStr">
         <is>
           <t>13:50:00</t>
         </is>
       </c>
-      <c r="AL3" t="n">
+      <c r="AL3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="n">
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AP3" s="2" t="inlineStr">
         <is>
           <t>13:40:23</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="n">
         <v>98.06999999999999</v>
       </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="n">
+      <c r="AW3" s="2" t="inlineStr"/>
+      <c r="AX3" s="2" t="inlineStr"/>
+      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AZ3" s="2" t="n">
         <v>20260216140501</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BA3" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 14:05:01</t>
         </is>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB3" s="2" t="n">
         <v>978</v>
       </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr">
+      <c r="BC3" s="2" t="inlineStr"/>
+      <c r="BD3" s="2" t="inlineStr"/>
+      <c r="BE3" s="2" t="inlineStr"/>
+      <c r="BF3" s="2" t="inlineStr"/>
+      <c r="BG3" s="2" t="inlineStr"/>
+      <c r="BH3" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1694,8 +2032,16 @@
   </sheetPr>
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECID</t>
@@ -1728,56 +2074,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>8725</v>
       </c>
-      <c r="D2" t="n">
-        <v>20260216162525</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="D2" s="2" t="n">
+        <v>20260216174410</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>8725</v>
       </c>
-      <c r="D3" t="n">
-        <v>20260216162531</v>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="D3" s="2" t="n">
+        <v>20260216174415</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
@@ -1785,6 +2131,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1796,269 +2145,2699 @@
   </sheetPr>
   <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>REQUEST_URL</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>BOARDID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>PRICE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>YIELDDATE</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ZCYCMOMENT</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>YIELDDATETYPE</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>EFFECTIVEYIELD</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>DURATION</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ZSPREADBP</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>GSPREADBP</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>WAPRICE</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>EFFECTIVEYIELDWAPRICE</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>DURATIONWAPRICE</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>IR</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ICPI</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>BEI</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>CBR</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>YIELDTOOFFER</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>YIELDLASTCOUPON</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>TRADEMOMENT</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>SEQNUM</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>SYSTIME</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/SU26238RMFS4.json</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>SU26238RMFS4</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>TQOB</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>60.005</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2041-05-15</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:29:54</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>MATDATE</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>13.7166</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>2785</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>-45</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>-80</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>60.119</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>13.689</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>2787</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:29:56</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>20260216174400</v>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 17:44:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/RU000A1041Q0.json</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>RU000A1041Q0</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>TQCB</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>98.12</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2031-10-28</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-13 18:49:59</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>MBS</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>18.759</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1038</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>394</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 15:03:08</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>20260216151800</v>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-16 15:18:00</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C140"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>SHEET_NAME</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>COLUMN_NAME</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>DESCRIPTION_RU</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
           <t>REQUEST_URL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>URL endpoint ISS, откуда получены данные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>SECID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Код финансового инструмента (ценной бумаги) в ISS MOEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>BOARDID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Идентификатор торгового режима/доски.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>SHORTNAME</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Сокращённое имя инструмента.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>PREVWAPRICE</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Предыдущая средневзвешенная цена.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>YIELDATPREVWAPRICE</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Доходность на базе предыдущей средневзвешенной цены.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>COUPONVALUE</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Размер купона за период.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>NEXTCOUPON</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Дата следующей купонной выплаты.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>ACCRUEDINT</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Накопленный купонный доход (НКД).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>PREVPRICE</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Предыдущая цена закрытия.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>LOTSIZE</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Размер стандартного лота.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>FACEVALUE</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Номинальная стоимость бумаги.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>BOARDNAME</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Название торгового режима/доски.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>STATUS</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Статус инструмента (например, A — активен).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>MATDATE</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>DECIMALS</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>COUPONPERIOD</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ISSUESIZE</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>PREVLEGALCLOSEPRICE</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Предыдущая официальная цена закрытия.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>PREVDATE</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>SECNAME</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Краткое наименование бумаги.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>REMARKS</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>MARKETCODE</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Код рынка.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>INSTRID</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Тип/класс инструмента.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>SECTORID</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Идентификатор сектора торгов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>MINSTEP</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>FACEUNIT</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>BUYBACKPRICE</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>BUYBACKDATE</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>ISIN</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Международный идентификационный код ценной бумаги.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>LATNAME</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Название бумаги латиницей.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>REGNUMBER</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Регистрационный номер выпуска.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>CURRENCYID</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Код валюты расчётов.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>ISSUESIZEPLACED</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>LISTLEVEL</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Уровень листинга MOEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>SECTYPE</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>COUPONPERCENT</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>OFFERDATE</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>SETTLEDATE</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>LOTVALUE</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>FACEVALUEONSETTLEDATE</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>CALLOPTIONDATE</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>PUTOPTIONDATE</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>DATEYIELDFROMISSUER</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>BONDTYPE</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>securities</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>BONDSUBTYPE</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>REQUEST_URL</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>URL endpoint ISS, откуда получены данные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Код финансового инструмента (ценной бумаги) в ISS MOEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>BIDDEPTH</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>OFFER</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>OFFERDEPTH</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>SPREAD</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>BIDDEPTHT</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>OFFERDEPTHT</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>LAST</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>LASTCHANGE</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>LASTCHANGEPRCNT</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>VALUE</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>YIELD</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>VALUE_USD</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>WAPRICE</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>LASTCNGTOLASTWAPRICE</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>WAPTOPREVWAPRICEPRCNT</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>WAPTOPREVWAPRICE</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>YIELDATWAPRICE</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>YIELDTOPREVYIELD</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>CLOSEYIELD</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>CLOSEPRICE</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>MARKETPRICETODAY</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>MARKETPRICE</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>LASTTOPREVPRICE</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>NUMTRADES</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>VOLTODAY</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>VALTODAY</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>VALTODAY_USD</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>BOARDID</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Идентификатор торгового режима/доски.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>TRADINGSTATUS</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>UPDATETIME</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>DURATION</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>NUMBIDS</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>NUMOFFERS</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>CHANGE</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>TIME</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>HIGHBID</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>LOWOFFER</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>PRICEMINUSPREVWAPRICE</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>LASTBID</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>LASTOFFER</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>LCURRENTPRICE</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>LCLOSEPRICE</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>MARKETPRICE2</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>OPENPERIODPRICE</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>SEQNUM</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>SYSTIME</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>VALTODAY_RUR</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>IRICPICLOSE</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>BEICLOSE</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>CBRCLOSE</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>YIELDTOOFFER</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>YIELDLASTCOUPON</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>TRADINGSESSION</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>CALLOPTIONYIELD</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>CALLOPTIONDURATION</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>ZSPREAD</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>marketdata</t>
+        </is>
+      </c>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>ZSPREADATWAPRICE</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
+        <is>
+          <t>dataversion</t>
+        </is>
+      </c>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>Код финансового инструмента (ценной бумаги) в ISS MOEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>dataversion</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>REQUEST_URL</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>URL endpoint ISS, откуда получены данные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
+        <is>
+          <t>dataversion</t>
+        </is>
+      </c>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>data_version</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>dataversion</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>seqnum</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>dataversion</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>trade_date</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>dataversion</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>trade_session_date</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>REQUEST_URL</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>URL endpoint ISS, откуда получены данные.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>SECID</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>Код финансового инструмента (ценной бумаги) в ISS MOEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>BOARDID</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>Идентификатор торгового режима/доски.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B121" s="3" t="inlineStr">
         <is>
           <t>PRICE</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B122" s="3" t="inlineStr">
         <is>
           <t>YIELDDATE</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>ZCYCMOMENT</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
         <is>
           <t>YIELDDATETYPE</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>EFFECTIVEYIELD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
         <is>
           <t>DURATION</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>ZSPREADBP</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
         <is>
           <t>GSPREADBP</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
         <is>
           <t>WAPRICE</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
         <is>
           <t>EFFECTIVEYIELDWAPRICE</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B131" s="3" t="inlineStr">
         <is>
           <t>DURATIONWAPRICE</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t>IR</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>ICPI</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>BEI</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
         <is>
           <t>CBR</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>YIELDTOOFFER</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>YIELDLASTCOUPON</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
         <is>
           <t>TRADEMOMENT</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
         <is>
           <t>SEQNUM</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
+        <is>
+          <t>marketdata_yields</t>
+        </is>
+      </c>
+      <c r="B140" s="3" t="inlineStr">
         <is>
           <t>SYSTIME</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/SU26238RMFS4.json</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SU26238RMFS4</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>TQOB</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>60.144</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2041-05-15</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:10:56</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MATDATE</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>13.683</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2788</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-46</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-78</v>
-      </c>
-      <c r="L2" t="n">
-        <v>60.124</v>
-      </c>
-      <c r="M2" t="n">
-        <v>13.6878</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2788</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:10:59</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>20260216162500</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>2026-02-16 16:25:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/RU000A1041Q0.json</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>RU000A1041Q0</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>TQCB</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>98.12</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2031-10-28</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-02-13 18:49:59</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MBS</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>18.759</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1038</v>
-      </c>
-      <c r="J3" t="n">
-        <v>394</v>
-      </c>
-      <c r="K3" t="n">
-        <v>385</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>2026-02-16 15:03:08</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>20260216151800</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2026-02-16 15:18:00</t>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>Описание не задано</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/endpoint_excels/iss__engines__engine__markets__market__securities__security.xlsx
+++ b/endpoint_excels/iss__engines__engine__markets__market__securities__security.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,16 +31,26 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -54,14 +64,31 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -137,6 +164,181 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TBL_01_iss__engines__engi" displayName="TBL_01_iss__engines__engi" ref="A1:AT3" headerRowCount="1">
+  <autoFilter ref="A1:AT3"/>
+  <tableColumns count="46">
+    <tableColumn id="1" name="REQUEST_URL"/>
+    <tableColumn id="2" name="SECID"/>
+    <tableColumn id="3" name="BOARDID"/>
+    <tableColumn id="4" name="SHORTNAME"/>
+    <tableColumn id="5" name="PREVWAPRICE"/>
+    <tableColumn id="6" name="YIELDATPREVWAPRICE"/>
+    <tableColumn id="7" name="COUPONVALUE"/>
+    <tableColumn id="8" name="NEXTCOUPON"/>
+    <tableColumn id="9" name="ACCRUEDINT"/>
+    <tableColumn id="10" name="PREVPRICE"/>
+    <tableColumn id="11" name="LOTSIZE"/>
+    <tableColumn id="12" name="FACEVALUE"/>
+    <tableColumn id="13" name="BOARDNAME"/>
+    <tableColumn id="14" name="STATUS"/>
+    <tableColumn id="15" name="MATDATE"/>
+    <tableColumn id="16" name="DECIMALS"/>
+    <tableColumn id="17" name="COUPONPERIOD"/>
+    <tableColumn id="18" name="ISSUESIZE"/>
+    <tableColumn id="19" name="PREVLEGALCLOSEPRICE"/>
+    <tableColumn id="20" name="PREVDATE"/>
+    <tableColumn id="21" name="SECNAME"/>
+    <tableColumn id="22" name="REMARKS"/>
+    <tableColumn id="23" name="MARKETCODE"/>
+    <tableColumn id="24" name="INSTRID"/>
+    <tableColumn id="25" name="SECTORID"/>
+    <tableColumn id="26" name="MINSTEP"/>
+    <tableColumn id="27" name="FACEUNIT"/>
+    <tableColumn id="28" name="BUYBACKPRICE"/>
+    <tableColumn id="29" name="BUYBACKDATE"/>
+    <tableColumn id="30" name="ISIN"/>
+    <tableColumn id="31" name="LATNAME"/>
+    <tableColumn id="32" name="REGNUMBER"/>
+    <tableColumn id="33" name="CURRENCYID"/>
+    <tableColumn id="34" name="ISSUESIZEPLACED"/>
+    <tableColumn id="35" name="LISTLEVEL"/>
+    <tableColumn id="36" name="SECTYPE"/>
+    <tableColumn id="37" name="COUPONPERCENT"/>
+    <tableColumn id="38" name="OFFERDATE"/>
+    <tableColumn id="39" name="SETTLEDATE"/>
+    <tableColumn id="40" name="LOTVALUE"/>
+    <tableColumn id="41" name="FACEVALUEONSETTLEDATE"/>
+    <tableColumn id="42" name="CALLOPTIONDATE"/>
+    <tableColumn id="43" name="PUTOPTIONDATE"/>
+    <tableColumn id="44" name="DATEYIELDFROMISSUER"/>
+    <tableColumn id="45" name="BONDTYPE"/>
+    <tableColumn id="46" name="BONDSUBTYPE"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="TBL_02_iss__engines__engi" displayName="TBL_02_iss__engines__engi" ref="A1:BL3" headerRowCount="1">
+  <autoFilter ref="A1:BL3"/>
+  <tableColumns count="64">
+    <tableColumn id="1" name="REQUEST_URL"/>
+    <tableColumn id="2" name="SECID"/>
+    <tableColumn id="3" name="BID"/>
+    <tableColumn id="4" name="BIDDEPTH"/>
+    <tableColumn id="5" name="OFFER"/>
+    <tableColumn id="6" name="OFFERDEPTH"/>
+    <tableColumn id="7" name="SPREAD"/>
+    <tableColumn id="8" name="BIDDEPTHT"/>
+    <tableColumn id="9" name="OFFERDEPTHT"/>
+    <tableColumn id="10" name="OPEN"/>
+    <tableColumn id="11" name="LOW"/>
+    <tableColumn id="12" name="HIGH"/>
+    <tableColumn id="13" name="LAST"/>
+    <tableColumn id="14" name="LASTCHANGE"/>
+    <tableColumn id="15" name="LASTCHANGEPRCNT"/>
+    <tableColumn id="16" name="QTY"/>
+    <tableColumn id="17" name="VALUE"/>
+    <tableColumn id="18" name="YIELD"/>
+    <tableColumn id="19" name="VALUE_USD"/>
+    <tableColumn id="20" name="WAPRICE"/>
+    <tableColumn id="21" name="LASTCNGTOLASTWAPRICE"/>
+    <tableColumn id="22" name="WAPTOPREVWAPRICEPRCNT"/>
+    <tableColumn id="23" name="WAPTOPREVWAPRICE"/>
+    <tableColumn id="24" name="YIELDATWAPRICE"/>
+    <tableColumn id="25" name="YIELDTOPREVYIELD"/>
+    <tableColumn id="26" name="CLOSEYIELD"/>
+    <tableColumn id="27" name="CLOSEPRICE"/>
+    <tableColumn id="28" name="MARKETPRICETODAY"/>
+    <tableColumn id="29" name="MARKETPRICE"/>
+    <tableColumn id="30" name="LASTTOPREVPRICE"/>
+    <tableColumn id="31" name="NUMTRADES"/>
+    <tableColumn id="32" name="VOLTODAY"/>
+    <tableColumn id="33" name="VALTODAY"/>
+    <tableColumn id="34" name="VALTODAY_USD"/>
+    <tableColumn id="35" name="BOARDID"/>
+    <tableColumn id="36" name="TRADINGSTATUS"/>
+    <tableColumn id="37" name="UPDATETIME"/>
+    <tableColumn id="38" name="DURATION"/>
+    <tableColumn id="39" name="NUMBIDS"/>
+    <tableColumn id="40" name="NUMOFFERS"/>
+    <tableColumn id="41" name="CHANGE"/>
+    <tableColumn id="42" name="TIME"/>
+    <tableColumn id="43" name="HIGHBID"/>
+    <tableColumn id="44" name="LOWOFFER"/>
+    <tableColumn id="45" name="PRICEMINUSPREVWAPRICE"/>
+    <tableColumn id="46" name="LASTBID"/>
+    <tableColumn id="47" name="LASTOFFER"/>
+    <tableColumn id="48" name="LCURRENTPRICE"/>
+    <tableColumn id="49" name="LCLOSEPRICE"/>
+    <tableColumn id="50" name="MARKETPRICE2"/>
+    <tableColumn id="51" name="OPENPERIODPRICE"/>
+    <tableColumn id="52" name="SEQNUM"/>
+    <tableColumn id="53" name="SYSTIME"/>
+    <tableColumn id="54" name="VALTODAY_RUR"/>
+    <tableColumn id="55" name="IRICPICLOSE"/>
+    <tableColumn id="56" name="BEICLOSE"/>
+    <tableColumn id="57" name="CBRCLOSE"/>
+    <tableColumn id="58" name="YIELDTOOFFER"/>
+    <tableColumn id="59" name="YIELDLASTCOUPON"/>
+    <tableColumn id="60" name="TRADINGSESSION"/>
+    <tableColumn id="61" name="CALLOPTIONYIELD"/>
+    <tableColumn id="62" name="CALLOPTIONDURATION"/>
+    <tableColumn id="63" name="ZSPREAD"/>
+    <tableColumn id="64" name="ZSPREADATWAPRICE"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="TBL_03_iss__engines__engi" displayName="TBL_03_iss__engines__engi" ref="A1:F3" headerRowCount="1">
+  <autoFilter ref="A1:F3"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="SECID"/>
+    <tableColumn id="2" name="REQUEST_URL"/>
+    <tableColumn id="3" name="data_version"/>
+    <tableColumn id="4" name="seqnum"/>
+    <tableColumn id="5" name="trade_date"/>
+    <tableColumn id="6" name="trade_session_date"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="TBL_04_iss__engines__engi" displayName="TBL_04_iss__engines__engi" ref="A1:W3" headerRowCount="1">
+  <autoFilter ref="A1:W3"/>
+  <tableColumns count="23">
+    <tableColumn id="1" name="REQUEST_URL"/>
+    <tableColumn id="2" name="SECID"/>
+    <tableColumn id="3" name="BOARDID"/>
+    <tableColumn id="4" name="PRICE"/>
+    <tableColumn id="5" name="YIELDDATE"/>
+    <tableColumn id="6" name="ZCYCMOMENT"/>
+    <tableColumn id="7" name="YIELDDATETYPE"/>
+    <tableColumn id="8" name="EFFECTIVEYIELD"/>
+    <tableColumn id="9" name="DURATION"/>
+    <tableColumn id="10" name="ZSPREADBP"/>
+    <tableColumn id="11" name="GSPREADBP"/>
+    <tableColumn id="12" name="WAPRICE"/>
+    <tableColumn id="13" name="EFFECTIVEYIELDWAPRICE"/>
+    <tableColumn id="14" name="DURATIONWAPRICE"/>
+    <tableColumn id="15" name="IR"/>
+    <tableColumn id="16" name="ICPI"/>
+    <tableColumn id="17" name="BEI"/>
+    <tableColumn id="18" name="CBR"/>
+    <tableColumn id="19" name="YIELDTOOFFER"/>
+    <tableColumn id="20" name="YIELDLASTCOUPON"/>
+    <tableColumn id="21" name="TRADEMOMENT"/>
+    <tableColumn id="22" name="SEQNUM"/>
+    <tableColumn id="23" name="SYSTIME"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -430,8 +632,56 @@
   </sheetPr>
   <dimension ref="A1:AT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="10" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="31" customWidth="1" min="31" max="31"/>
+    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="17" customWidth="1" min="34" max="34"/>
+    <col width="11" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="23" customWidth="1" min="41" max="41"/>
+    <col width="16" customWidth="1" min="42" max="42"/>
+    <col width="15" customWidth="1" min="43" max="43"/>
+    <col width="21" customWidth="1" min="44" max="44"/>
+    <col width="26" customWidth="1" min="45" max="45"/>
+    <col width="14" customWidth="1" min="46" max="46"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>REQUEST_URL</t>
@@ -664,344 +914,344 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>TQOB</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>ОФЗ 26238</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="2" t="n">
         <v>59.061</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="2" t="n">
         <v>13.95</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="2" t="n">
         <v>35.4</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>14.78</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>59.549</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Т+: Гособлигации - безадрес.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>2041-05-15</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>182</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="2" t="n">
         <v>750000000</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="2" t="n">
         <v>59.549</v>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>ОФЗ-ПД 26238 15/05/2041</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>FNDT</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>GOFZ</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="n">
         <v>0.001</v>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>SUR</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>0000-00-00</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>RU000A1038V6</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>OFZ-PD 26238</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>26238RMFS</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>SUR</t>
         </is>
       </c>
-      <c r="AH2" t="n">
+      <c r="AH2" s="2" t="n">
         <v>722071798</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AI2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AK2" t="n">
+      <c r="AK2" s="2" t="n">
         <v>7.1</v>
       </c>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr">
+      <c r="AL2" s="2" t="inlineStr"/>
+      <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="AN2" t="n">
+      <c r="AN2" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AO2" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr"/>
+      <c r="AQ2" s="2" t="inlineStr"/>
+      <c r="AR2" s="2" t="inlineStr"/>
+      <c r="AS2" s="2" t="inlineStr">
         <is>
           <t>Фикс с известным купоном</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AT2" s="2" t="inlineStr">
         <is>
           <t>До погашения</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>ИАДОМ 1P13</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="2" t="n">
         <v>98.12</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="2" t="n">
         <v>18.76</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="2" t="n">
         <v>7.05</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>4.55</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="2" t="n">
         <v>98.12</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="2" t="n">
         <v>498.52</v>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Т+: Облигации - безадрес.</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>2031-10-28</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>31</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="2" t="n">
         <v>5353129</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="2" t="n">
         <v>98.12</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>ДОМ.РФ Ипотечный агент БО 1P13</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>FNDT</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>EICB</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="n">
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="n">
         <v>0.01</v>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA3" s="2" t="inlineStr">
         <is>
           <t>SUR</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr">
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>2031-10-28</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AE3" s="2" t="inlineStr">
         <is>
           <t>DOM.RF Mortgage agent BO 1P13</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AF3" s="2" t="inlineStr">
         <is>
           <t>4B02-13-00307-R-001P</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG3" s="2" t="inlineStr">
         <is>
           <t>SUR</t>
         </is>
       </c>
-      <c r="AH3" t="n">
+      <c r="AH3" s="2" t="n">
         <v>5353129</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AI3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AJ3" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AK3" t="n">
+      <c r="AK3" s="2" t="n">
         <v>16.65</v>
       </c>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr">
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr">
         <is>
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="AN3" t="n">
+      <c r="AN3" s="2" t="n">
         <v>498.52</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AO3" s="2" t="n">
         <v>498.52</v>
       </c>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr">
+      <c r="AP3" s="2" t="inlineStr"/>
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr">
         <is>
           <t>Флоатер</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AT3" s="2" t="inlineStr">
         <is>
           <t>До погашения</t>
         </is>
@@ -1009,6 +1259,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1020,8 +1273,74 @@
   </sheetPr>
   <dimension ref="A1:BL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="18" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="18" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="14" customWidth="1" min="34" max="34"/>
+    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="15" customWidth="1" min="36" max="36"/>
+    <col width="12" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="10" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="10" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="23" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="11" customWidth="1" min="47" max="47"/>
+    <col width="15" customWidth="1" min="48" max="48"/>
+    <col width="13" customWidth="1" min="49" max="49"/>
+    <col width="14" customWidth="1" min="50" max="50"/>
+    <col width="17" customWidth="1" min="51" max="51"/>
+    <col width="16" customWidth="1" min="52" max="52"/>
+    <col width="21" customWidth="1" min="53" max="53"/>
+    <col width="14" customWidth="1" min="54" max="54"/>
+    <col width="13" customWidth="1" min="55" max="55"/>
+    <col width="10" customWidth="1" min="56" max="56"/>
+    <col width="10" customWidth="1" min="57" max="57"/>
+    <col width="14" customWidth="1" min="58" max="58"/>
+    <col width="17" customWidth="1" min="59" max="59"/>
+    <col width="16" customWidth="1" min="60" max="60"/>
+    <col width="17" customWidth="1" min="61" max="61"/>
+    <col width="20" customWidth="1" min="62" max="62"/>
+    <col width="10" customWidth="1" min="63" max="63"/>
+    <col width="18" customWidth="1" min="64" max="64"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>REQUEST_URL</t>
@@ -1344,345 +1663,348 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>59.825</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
+      <c r="D2" s="2" t="inlineStr"/>
+      <c r="E2" s="2" t="n">
         <v>59.847</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="n">
         <v>0.022</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="2" t="n">
         <v>336305</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>454941</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>59.697</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="2" t="n">
         <v>59.605</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>60.6</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="2" t="n">
         <v>59.847</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="2" t="n">
         <v>0.022</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="2" t="n">
         <v>598.47</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="2" t="n">
         <v>13.76</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="2" t="n">
         <v>7.75</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="2" t="n">
         <v>60.1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U2" s="2" t="n">
         <v>0.786</v>
       </c>
-      <c r="V2" t="n">
+      <c r="V2" s="2" t="n">
         <v>1.76</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W2" s="2" t="n">
         <v>1.039</v>
       </c>
-      <c r="X2" t="n">
+      <c r="X2" s="2" t="n">
         <v>13.69</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y2" s="2" t="n">
         <v>-0.26</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="Z2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="n">
         <v>59.045</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AD2" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AE2" s="2" t="n">
         <v>38289</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AF2" s="2" t="n">
         <v>3533131</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AG2" s="2" t="n">
         <v>2123419506</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AH2" s="2" t="n">
         <v>27507429</v>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>TQOB</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AJ2" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
+      <c r="AK2" s="2" t="inlineStr">
         <is>
           <t>18:01:18</t>
         </is>
       </c>
-      <c r="AL2" t="n">
+      <c r="AL2" s="2" t="n">
         <v>2788</v>
       </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
+      <c r="AM2" s="2" t="inlineStr"/>
+      <c r="AN2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="n">
         <v>0.298</v>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="AP2" s="2" t="inlineStr">
         <is>
           <t>18:01:18</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
+      <c r="AQ2" s="2" t="inlineStr"/>
+      <c r="AR2" s="2" t="inlineStr"/>
+      <c r="AS2" s="2" t="n">
         <v>0.786</v>
       </c>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
+      <c r="AT2" s="2" t="inlineStr"/>
+      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="n">
         <v>59.837</v>
       </c>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="n">
+      <c r="AW2" s="2" t="inlineStr"/>
+      <c r="AX2" s="2" t="inlineStr"/>
+      <c r="AY2" s="2" t="n">
         <v>59.697</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="AZ2" s="2" t="n">
         <v>20260216181618</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BA2" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:18</t>
         </is>
       </c>
-      <c r="BB2" t="n">
+      <c r="BB2" s="2" t="n">
         <v>2123419506</v>
       </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr">
+      <c r="BC2" s="2" t="inlineStr"/>
+      <c r="BD2" s="2" t="inlineStr"/>
+      <c r="BE2" s="2" t="inlineStr"/>
+      <c r="BF2" s="2" t="inlineStr"/>
+      <c r="BG2" s="2" t="inlineStr"/>
+      <c r="BH2" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="n">
+      <c r="BI2" s="2" t="inlineStr"/>
+      <c r="BJ2" s="2" t="inlineStr"/>
+      <c r="BK2" s="2" t="n">
         <v>-0.44</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BL2" s="2" t="n">
         <v>-0.5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>98.06</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="n">
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n">
         <v>98.11</v>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="n">
         <v>0.05</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="2" t="n">
         <v>6166</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>6314</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="2" t="n">
         <v>98.06999999999999</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="2" t="n">
         <v>98.06</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="2" t="n">
         <v>98.06999999999999</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="2" t="n">
         <v>98.06</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="2" t="n">
         <v>488.85</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="2" t="n">
         <v>6.33</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="2" t="n">
         <v>98.06999999999999</v>
       </c>
-      <c r="U3" t="n">
+      <c r="U3" s="2" t="n">
         <v>-0.06</v>
       </c>
-      <c r="V3" t="n">
+      <c r="V3" s="2" t="n">
         <v>-0.05</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W3" s="2" t="n">
         <v>-0.05</v>
       </c>
-      <c r="X3" t="n">
+      <c r="X3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="Z3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="n">
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="n">
         <v>97.94</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AD3" s="2" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AE3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AF3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AG3" s="2" t="n">
         <v>978</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AH3" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AI3" s="2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AJ3" s="2" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AK3" s="2" t="inlineStr">
         <is>
           <t>13:50:00</t>
         </is>
       </c>
-      <c r="AL3" t="n">
+      <c r="AL3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="n">
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AP3" s="2" t="inlineStr">
         <is>
           <t>13:40:23</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="n">
+      <c r="AQ3" s="2" t="inlineStr"/>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="n">
         <v>-0.06</v>
       </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="n">
+      <c r="AT3" s="2" t="inlineStr"/>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="n">
         <v>98.06999999999999</v>
       </c>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="n">
+      <c r="AW3" s="2" t="inlineStr"/>
+      <c r="AX3" s="2" t="inlineStr"/>
+      <c r="AY3" s="2" t="inlineStr"/>
+      <c r="AZ3" s="2" t="n">
         <v>20260216140501</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BA3" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 14:05:01</t>
         </is>
       </c>
-      <c r="BB3" t="n">
+      <c r="BB3" s="2" t="n">
         <v>978</v>
       </c>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr">
+      <c r="BC3" s="2" t="inlineStr"/>
+      <c r="BD3" s="2" t="inlineStr"/>
+      <c r="BE3" s="2" t="inlineStr"/>
+      <c r="BF3" s="2" t="inlineStr"/>
+      <c r="BG3" s="2" t="inlineStr"/>
+      <c r="BH3" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
+      <c r="BI3" s="2" t="inlineStr"/>
+      <c r="BJ3" s="2" t="inlineStr"/>
+      <c r="BK3" s="2" t="inlineStr"/>
+      <c r="BL3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1694,8 +2016,16 @@
   </sheetPr>
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SECID</t>
@@ -1728,56 +2058,56 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="2" t="n">
         <v>8725</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>20260216181615</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="2" t="n">
         <v>8725</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>20260216181620</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
@@ -1785,6 +2115,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1796,8 +2129,33 @@
   </sheetPr>
   <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="21" customWidth="1" min="23" max="23"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>REQUEST_URL</t>
@@ -1915,144 +2273,144 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/SU26238RMFS4.json</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SU26238RMFS4</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>TQOB</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="2" t="n">
         <v>59.847</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2041-05-15</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:01:56</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>MATDATE</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="2" t="n">
         <v>13.755</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="2" t="n">
         <v>2781</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="2" t="n">
         <v>-44</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="2" t="n">
         <v>-77</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="2" t="n">
         <v>60.1</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="2" t="n">
         <v>13.6936</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2" s="2" t="n">
         <v>2787</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:01:58</t>
         </is>
       </c>
-      <c r="V2" t="n">
+      <c r="V2" s="2" t="n">
         <v>20260216181600</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 18:16:00</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>https://iss.moex.com/iss/engines/stock/markets/bonds/securities/RU000A1041Q0.json</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>RU000A1041Q0</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>TQCB</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="2" t="n">
         <v>98.12</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2031-10-28</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-02-13 18:49:59</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>MBS</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="2" t="n">
         <v>18.759</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="2" t="n">
         <v>1038</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="2" t="n">
         <v>394</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" s="2" t="inlineStr"/>
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 15:03:08</t>
         </is>
       </c>
-      <c r="V3" t="n">
+      <c r="V3" s="2" t="n">
         <v>20260216151800</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W3" s="2" t="inlineStr">
         <is>
           <t>2026-02-16 15:18:00</t>
         </is>
@@ -2060,5 +2418,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>